--- a/#Police_anonymized.xlsx
+++ b/#Police_anonymized.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11285,7 +11285,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="J586" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -20485,7 +20485,7 @@
       </c>
       <c r="J587" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20527,7 +20527,7 @@
       </c>
       <c r="J588" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="J589" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -20611,7 +20611,7 @@
       </c>
       <c r="J590" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20653,7 +20653,7 @@
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20695,7 +20695,7 @@
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20739,7 +20739,7 @@
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20783,7 +20783,7 @@
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20825,7 @@
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -20909,7 +20909,7 @@
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -20993,7 +20993,7 @@
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25457,7 +25457,7 @@
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25500,7 +25500,7 @@
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32019,7 +32019,7 @@
       </c>
       <c r="J923" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32061,7 +32061,7 @@
       </c>
       <c r="J924" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32100,7 +32100,7 @@
       </c>
       <c r="J925" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32139,7 +32139,7 @@
       </c>
       <c r="J926" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32177,7 +32177,7 @@
       </c>
       <c r="J927" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32215,7 +32215,7 @@
       </c>
       <c r="J928" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32254,7 +32254,7 @@
       </c>
       <c r="J929" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -32292,7 +32292,7 @@
       </c>
       <c r="J930" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="J931" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32370,7 +32370,7 @@
       </c>
       <c r="J932" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32408,7 +32408,7 @@
       </c>
       <c r="J933" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -32446,7 +32446,7 @@
       </c>
       <c r="J934" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="J935" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32525,7 +32525,7 @@
       </c>
       <c r="J936" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32565,7 +32565,7 @@
       </c>
       <c r="J937" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32604,7 +32604,7 @@
       </c>
       <c r="J938" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32643,7 +32643,7 @@
       </c>
       <c r="J939" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -32681,7 +32681,7 @@
       </c>
       <c r="J940" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -32721,7 +32721,7 @@
       </c>
       <c r="J941" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
